--- a/PartialRefundDataUpgrade.xlsx
+++ b/PartialRefundDataUpgrade.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SoapData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A708B65-CEB7-4954-9D53-DC5FBA2D0216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A86588B6-8EAE-4EBB-A478-51F81EAB3128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1270" yWindow="2430" windowWidth="31880" windowHeight="14900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SaleUpgrade" sheetId="2" r:id="rId1"/>
@@ -333,9 +333,6 @@
     <t>22201</t>
   </si>
   <si>
-    <t>12/25</t>
-  </si>
-  <si>
     <t>RefundResultCode</t>
   </si>
   <si>
@@ -349,6 +346,9 @@
   </si>
   <si>
     <t>iahmed@govolution.com</t>
+  </si>
+  <si>
+    <t>12/29</t>
   </si>
 </sst>
 </file>
@@ -399,10 +399,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -684,83 +683,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BW5"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="31.3828125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.3828125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.53515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.53515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.3828125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.15234375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="13.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="11.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="6.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="10.15234375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.53125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.53125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="11.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="10.1328125" style="1" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="12.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="11.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="5.3828125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="9.15234375" style="1"/>
-    <col min="41" max="41" width="8.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="11.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="5.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="9.1328125" style="1"/>
+    <col min="41" max="41" width="8.86328125" style="1" bestFit="1" customWidth="1"/>
     <col min="42" max="42" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="12.15234375" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="11.53515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="10.3828125" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="14.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="17.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="15.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="19.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="6.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="10.15234375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="12.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="11.53125" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="10.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="14.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="19.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="10.1328125" style="1" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="12.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="11.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="5.3828125" style="1" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="24.53515625" style="1" customWidth="1"/>
+    <col min="53" max="53" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="11.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="5.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="24.53125" style="1" customWidth="1"/>
     <col min="57" max="57" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="16.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="12.3046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="16.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="60" max="60" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="14.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="14.86328125" style="1" bestFit="1" customWidth="1"/>
     <col min="62" max="62" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="12.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="11.69140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="12.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="65" max="65" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="10.53515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="17.53515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="14.15234375" style="1" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="12.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="11.15234375" style="1" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="24.3828125" style="1" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="7.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="73" max="16384" width="9.15234375" style="1"/>
+    <col min="66" max="66" width="10.53125" style="1" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="17.53125" style="1" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="14.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="12.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="11.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="24.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="73" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:75" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -978,16 +977,16 @@
         <v>82</v>
       </c>
       <c r="BU1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="BV1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BW1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="BW1" s="1" t="s">
-        <v>105</v>
-      </c>
     </row>
-    <row r="2" spans="1:75" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>79</v>
       </c>
@@ -1039,8 +1038,8 @@
       <c r="BB2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="BD2" s="2" t="s">
-        <v>107</v>
+      <c r="BD2" t="s">
+        <v>106</v>
       </c>
       <c r="BE2" s="1" t="s">
         <v>101</v>
@@ -1049,7 +1048,7 @@
         <v>145</v>
       </c>
       <c r="BN2" s="1" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="BO2" s="1" t="s">
         <v>78</v>
@@ -1070,7 +1069,7 @@
         <v>84</v>
       </c>
       <c r="BU2" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="BV2" s="1" t="s">
         <v>83</v>
@@ -1079,7 +1078,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:75" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>91</v>
       </c>
@@ -1131,8 +1130,8 @@
       <c r="BB3" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="BD3" s="2" t="s">
-        <v>107</v>
+      <c r="BD3" t="s">
+        <v>106</v>
       </c>
       <c r="BE3" s="1" t="s">
         <v>101</v>
@@ -1165,7 +1164,7 @@
         <v>84</v>
       </c>
       <c r="BU3" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="BV3" s="1" t="s">
         <v>83</v>
@@ -1174,7 +1173,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:75" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>92</v>
       </c>
@@ -1226,8 +1225,8 @@
       <c r="BB4" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="BD4" s="2" t="s">
-        <v>107</v>
+      <c r="BD4" t="s">
+        <v>106</v>
       </c>
       <c r="BE4" s="1" t="s">
         <v>101</v>
@@ -1260,7 +1259,7 @@
         <v>84</v>
       </c>
       <c r="BU4" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="BV4" s="1" t="s">
         <v>83</v>
@@ -1269,7 +1268,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:75" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>93</v>
       </c>
@@ -1315,8 +1314,8 @@
       <c r="AW5" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="BD5" s="2" t="s">
-        <v>107</v>
+      <c r="BD5" t="s">
+        <v>106</v>
       </c>
       <c r="BE5" s="1" t="s">
         <v>101</v>
@@ -1355,7 +1354,7 @@
         <v>84</v>
       </c>
       <c r="BU5" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="BV5" s="1" t="s">
         <v>83</v>
